--- a/branches/release-candidate/StructureDefinition-be-medicationdispense.xlsx
+++ b/branches/release-candidate/StructureDefinition-be-medicationdispense.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4620" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4620" uniqueCount="707">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T08:07:39+00:00</t>
+    <t>2026-03-27T06:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -367,7 +367,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -611,7 +611,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -926,7 +926,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -951,7 +951,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -1001,7 +1001,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -1016,7 +1016,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -1040,7 +1040,7 @@
     <t>A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -1050,7 +1050,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Medication)</t>
+Reference(Medication|4.0.1)</t>
   </si>
   <si>
     <t>What medication was supplied</t>
@@ -1065,7 +1065,7 @@
     <t>A coded concept identifying which substance or product can be dispensed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -1099,6 +1099,9 @@
     <t>The drug code. For example CNK code for the medication</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+  </si>
+  <si>
     <t>MedicationDispense.medication[x]:medicationReference</t>
   </si>
   <si>
@@ -1140,7 +1143,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1197,7 +1200,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1308,7 +1311,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1381,7 +1384,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1424,7 +1427,7 @@
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1440,7 +1443,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1507,7 +1510,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1602,7 +1605,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
@@ -1730,7 +1733,7 @@
     <t>A coded concept identifying additional instructions such as "take with water" or "avoid operating heavy machinery".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/additional-instruction-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.additionalInstruction</t>
@@ -1795,7 +1798,7 @@
     <t>A coded concept identifying the precondition that should be met or evaluated prior to consuming or administering a medication dose.  For example "pain", "30 minutes prior to sexual intercourse", "on flare-up" etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>Dosage.asNeeded[x]</t>
@@ -1825,7 +1828,7 @@
     <t>A coded concept describing the site location the medicine enters into or onto the body.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/approach-site-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/approach-site-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -1852,7 +1855,7 @@
     <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.route</t>
@@ -1882,7 +1885,7 @@
     <t>A coded concept describing the technique by which the medicine is administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.method</t>
@@ -1934,7 +1937,7 @@
     <t>The kind of dose or rate specified.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/dose-rate-type</t>
+    <t>http://hl7.org/fhir/ValueSet/dose-rate-type|4.0.1</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.type</t>
@@ -1947,7 +1950,7 @@
   </si>
   <si>
     <t>Range
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>Amount of medication per dose</t>
@@ -1972,7 +1975,7 @@
   </si>
   <si>
     <t>Ratio
-RangeQuantity {SimpleQuantity}</t>
+RangeQuantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>Amount of medication per unit of time</t>
@@ -2143,7 +2146,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2166,7 +2169,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2185,7 +2188,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2524,17 +2527,17 @@
   <dimension ref="A1:AO124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="62.16015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="62.16015625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.47265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.29296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.29296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="166.0390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="142.3515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2543,26 +2546,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="198.02734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3857,7 +3860,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>156</v>
       </c>
@@ -6784,7 +6787,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>348</v>
       </c>
@@ -6855,7 +6858,7 @@
         <v>350</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>78</v>
@@ -6903,15 +6906,15 @@
         <v>347</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>334</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>78</v>
@@ -6933,7 +6936,7 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>336</v>
@@ -7022,12 +7025,12 @@
         <v>347</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7050,16 +7053,16 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7109,7 +7112,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7124,27 +7127,27 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7167,13 +7170,13 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7224,7 +7227,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7239,10 +7242,10 @@
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>78</v>
@@ -7256,10 +7259,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7371,10 +7374,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7488,10 +7491,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7517,13 +7520,13 @@
         <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7573,7 +7576,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7582,7 +7585,7 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>100</v>
@@ -7605,10 +7608,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7634,13 +7637,13 @@
         <v>102</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7669,10 +7672,10 @@
         <v>189</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7690,7 +7693,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7720,12 +7723,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7751,13 +7754,13 @@
         <v>146</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7807,7 +7810,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7825,7 +7828,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7839,10 +7842,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7954,10 +7957,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8071,10 +8074,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8190,10 +8193,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8309,10 +8312,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8424,10 +8427,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8541,10 +8544,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8660,10 +8663,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8775,10 +8778,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8892,10 +8895,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8940,7 +8943,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -9011,10 +9014,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9128,10 +9131,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9174,7 +9177,7 @@
         <v>78</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>78</v>
@@ -9245,10 +9248,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9362,10 +9365,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9481,10 +9484,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9600,10 +9603,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9648,7 +9651,7 @@
         <v>78</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>272</v>
@@ -9719,10 +9722,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9836,10 +9839,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9951,10 +9954,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10068,10 +10071,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10097,13 +10100,13 @@
         <v>160</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10153,7 +10156,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10185,10 +10188,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10211,13 +10214,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10268,7 +10271,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10286,10 +10289,10 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -10298,12 +10301,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10326,13 +10329,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10383,7 +10386,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10398,10 +10401,10 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -10415,10 +10418,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10530,10 +10533,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10647,14 +10650,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10676,10 +10679,10 @@
         <v>134</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>137</v>
@@ -10734,7 +10737,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10766,10 +10769,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10795,14 +10798,14 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10830,10 +10833,10 @@
         <v>322</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10851,7 +10854,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10869,7 +10872,7 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
@@ -10883,10 +10886,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10998,10 +11001,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11115,10 +11118,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11234,10 +11237,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11282,7 +11285,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>78</v>
@@ -11353,10 +11356,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11379,13 +11382,13 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11436,7 +11439,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>88</v>
@@ -11451,10 +11454,10 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -11468,10 +11471,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11494,13 +11497,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11551,7 +11554,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11569,7 +11572,7 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
@@ -11581,12 +11584,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11609,16 +11612,16 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11668,7 +11671,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11683,27 +11686,27 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11815,10 +11818,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11932,10 +11935,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11961,13 +11964,13 @@
         <v>160</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12017,7 +12020,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12026,7 +12029,7 @@
         <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>100</v>
@@ -12049,10 +12052,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12078,13 +12081,13 @@
         <v>102</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12113,10 +12116,10 @@
         <v>189</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -12134,7 +12137,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12164,12 +12167,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12195,13 +12198,13 @@
         <v>146</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12251,7 +12254,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12269,7 +12272,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -12281,12 +12284,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12312,13 +12315,13 @@
         <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12368,7 +12371,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12400,10 +12403,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12429,10 +12432,10 @@
         <v>184</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12462,10 +12465,10 @@
         <v>322</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -12483,7 +12486,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12501,24 +12504,24 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12541,13 +12544,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12598,7 +12601,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12616,24 +12619,24 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12656,13 +12659,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12713,7 +12716,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12731,7 +12734,7 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12740,15 +12743,15 @@
         <v>78</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12771,13 +12774,13 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12828,7 +12831,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12846,24 +12849,24 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12886,13 +12889,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12943,7 +12946,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12958,27 +12961,27 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13001,13 +13004,13 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13058,7 +13061,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13076,24 +13079,24 @@
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13116,13 +13119,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13173,7 +13176,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13191,24 +13194,24 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13231,13 +13234,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13288,7 +13291,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13303,10 +13306,10 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>78</v>
@@ -13315,15 +13318,15 @@
         <v>78</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13346,16 +13349,16 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13405,7 +13408,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13423,7 +13426,7 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -13437,10 +13440,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13552,10 +13555,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13669,14 +13672,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13698,10 +13701,10 @@
         <v>134</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>137</v>
@@ -13756,7 +13759,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13788,10 +13791,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13814,17 +13817,17 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13873,7 +13876,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13891,7 +13894,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13900,15 +13903,15 @@
         <v>78</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13934,14 +13937,14 @@
         <v>160</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13990,7 +13993,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -14008,7 +14011,7 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -14017,15 +14020,15 @@
         <v>78</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14051,16 +14054,16 @@
         <v>184</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -14088,10 +14091,10 @@
         <v>322</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
@@ -14109,7 +14112,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -14127,7 +14130,7 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>78</v>
@@ -14136,15 +14139,15 @@
         <v>78</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14170,10 +14173,10 @@
         <v>160</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -14224,7 +14227,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14242,7 +14245,7 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -14251,15 +14254,15 @@
         <v>78</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14282,19 +14285,19 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14343,7 +14346,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14361,7 +14364,7 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>78</v>
@@ -14375,10 +14378,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14401,16 +14404,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14439,10 +14442,10 @@
         <v>322</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -14460,7 +14463,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14478,7 +14481,7 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -14487,15 +14490,15 @@
         <v>78</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14521,16 +14524,16 @@
         <v>184</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14558,10 +14561,10 @@
         <v>322</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14579,7 +14582,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14597,7 +14600,7 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>78</v>
@@ -14606,15 +14609,15 @@
         <v>78</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14640,14 +14643,14 @@
         <v>184</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14675,10 +14678,10 @@
         <v>322</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -14696,7 +14699,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14714,7 +14717,7 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -14723,15 +14726,15 @@
         <v>78</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14757,16 +14760,16 @@
         <v>184</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14794,10 +14797,10 @@
         <v>322</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -14815,7 +14818,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14833,7 +14836,7 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>78</v>
@@ -14842,15 +14845,15 @@
         <v>78</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14873,13 +14876,13 @@
         <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14930,7 +14933,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14957,15 +14960,15 @@
         <v>78</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15077,10 +15080,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15194,10 +15197,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15223,14 +15226,14 @@
         <v>184</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -15258,10 +15261,10 @@
         <v>322</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15279,7 +15282,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15306,15 +15309,15 @@
         <v>78</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15337,19 +15340,19 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -15398,7 +15401,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15416,7 +15419,7 @@
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>78</v>
@@ -15425,15 +15428,15 @@
         <v>78</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15456,19 +15459,19 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15517,7 +15520,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15535,7 +15538,7 @@
         <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>78</v>
@@ -15544,15 +15547,15 @@
         <v>78</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15575,19 +15578,19 @@
         <v>89</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>78</v>
@@ -15636,7 +15639,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15654,7 +15657,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>78</v>
@@ -15663,15 +15666,15 @@
         <v>78</v>
       </c>
       <c r="AO112" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15694,19 +15697,19 @@
         <v>89</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15755,7 +15758,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15773,7 +15776,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>78</v>
@@ -15787,10 +15790,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15813,17 +15816,17 @@
         <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15872,7 +15875,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15890,7 +15893,7 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>78</v>
@@ -15904,10 +15907,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15930,13 +15933,13 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15987,7 +15990,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16005,13 +16008,13 @@
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>78</v>
@@ -16019,10 +16022,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16134,10 +16137,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16251,14 +16254,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16280,10 +16283,10 @@
         <v>134</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>137</v>
@@ -16338,7 +16341,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16370,10 +16373,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16399,10 +16402,10 @@
         <v>248</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16453,7 +16456,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>88</v>
@@ -16471,7 +16474,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>78</v>
@@ -16485,10 +16488,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16514,10 +16517,10 @@
         <v>184</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16547,10 +16550,10 @@
         <v>322</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>78</v>
@@ -16568,7 +16571,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16586,24 +16589,24 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AO120" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16629,10 +16632,10 @@
         <v>184</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16662,10 +16665,10 @@
         <v>322</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>78</v>
@@ -16683,7 +16686,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16701,13 +16704,13 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>78</v>
@@ -16715,10 +16718,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16741,13 +16744,13 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16798,7 +16801,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16816,13 +16819,13 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>78</v>
@@ -16830,14 +16833,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16856,16 +16859,16 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -16915,7 +16918,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16933,7 +16936,7 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>78</v>
@@ -16947,10 +16950,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16973,16 +16976,16 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -17032,7 +17035,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17050,7 +17053,7 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>78</v>
@@ -17064,12 +17067,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO124">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
